--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.24507280322799</v>
+        <v>0.5273243305245484</v>
       </c>
       <c r="D2" t="n">
-        <v>3.080466841420892</v>
+        <v>0.5005758617308951</v>
       </c>
       <c r="E2" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F2" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.32651805104652</v>
+        <v>7.690559183295059</v>
       </c>
       <c r="D3" t="n">
-        <v>47.35631666019061</v>
+        <v>7.695401457280974</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.52956286291941</v>
+        <v>4.473553965224403</v>
       </c>
       <c r="D4" t="n">
-        <v>27.40678439111648</v>
+        <v>4.453602463556428</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F4" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.70661383547646</v>
+        <v>6.127324748264925</v>
       </c>
       <c r="D5" t="n">
-        <v>37.66472700709318</v>
+        <v>6.120518138652643</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F5" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.90249264378807</v>
+        <v>7.296655054615562</v>
       </c>
       <c r="D6" t="n">
-        <v>44.83130797840127</v>
+        <v>7.285087546490207</v>
       </c>
       <c r="E6" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F6" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.62508383739836</v>
+        <v>5.301576123577235</v>
       </c>
       <c r="D7" t="n">
-        <v>32.26254768585162</v>
+        <v>5.242663998950889</v>
       </c>
       <c r="E7" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F7" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.24467536050172</v>
+        <v>5.077259746081529</v>
       </c>
       <c r="D8" t="n">
-        <v>31.40214556625819</v>
+        <v>5.102848654516957</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F8" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.62779308670556</v>
+        <v>6.602016376589654</v>
       </c>
       <c r="D9" t="n">
-        <v>40.34598842187118</v>
+        <v>6.556223118554067</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F9" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.37556275503309</v>
+        <v>8.023528947692878</v>
       </c>
       <c r="D10" t="n">
-        <v>49.67650595548968</v>
+        <v>8.072432217767073</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F10" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.99945595007063</v>
+        <v>4.874911591886477</v>
       </c>
       <c r="D11" t="n">
-        <v>29.79481024197678</v>
+        <v>4.841656664321227</v>
       </c>
       <c r="E11" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F11" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.85210570419611</v>
+        <v>3.388467176931869</v>
       </c>
       <c r="D12" t="n">
-        <v>21.21336532505125</v>
+        <v>3.447171865320827</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F12" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.18189332097821</v>
+        <v>6.204557664658959</v>
       </c>
       <c r="D13" t="n">
-        <v>37.98052230707508</v>
+        <v>6.1718348748997</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F13" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.12342122079936</v>
+        <v>3.107555948379896</v>
       </c>
       <c r="D14" t="n">
-        <v>19.05690016546292</v>
+        <v>3.096746276887724</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F14" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.6442427434477</v>
+        <v>6.767189445810251</v>
       </c>
       <c r="D15" t="n">
-        <v>42.00926699146798</v>
+        <v>6.826505886113547</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F15" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.50165053520194</v>
+        <v>2.681518211970315</v>
       </c>
       <c r="D16" t="n">
-        <v>16.32830711135368</v>
+        <v>2.653349905594973</v>
       </c>
       <c r="E16" t="n">
-        <v>12.4459913582455</v>
+        <v>2.022473595714894</v>
       </c>
       <c r="F16" t="n">
-        <v>12.49748465706231</v>
+        <v>2.030841256772626</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
